--- a/src/test/resources/testdata/TestData.xlsx
+++ b/src/test/resources/testdata/TestData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Automation\EnterpriseAutomation\src\test\resources\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2854C770-01AC-4367-929C-F7DBC00AE231}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FD254B9-78A5-4FA1-8BA6-B9343673928D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="20985" xr2:uid="{94DB17ED-B2F1-44BA-BCCB-694A5169B770}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="21">
   <si>
     <t>Execute</t>
   </si>
@@ -82,6 +82,12 @@
   </si>
   <si>
     <t>Menu</t>
+  </si>
+  <si>
+    <t>ValidLoginTest_About</t>
+  </si>
+  <si>
+    <t>About page</t>
   </si>
 </sst>
 </file>
@@ -449,11 +455,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A0C82D7-3FCE-4585-9D9C-EF123EBA3D80}">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.28515625" customWidth="1"/>
     <col min="3" max="3" width="15.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="35.42578125" bestFit="1" customWidth="1"/>
@@ -544,6 +550,23 @@
         <v>18</v>
       </c>
     </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
